--- a/public/templates/master-data-template.xlsx
+++ b/public/templates/master-data-template.xlsx
@@ -8,80 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A1F0AC-91AC-4359-9E85-9A6EF55E2D9D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DF88F8-04A4-43CE-8A54-86CBBBC085F5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12108" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grades_Sections" sheetId="1" r:id="rId1"/>
-    <sheet name="Subjects" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="Grade_Schedules" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>Grade Level</t>
   </si>
   <si>
     <t>Section Name</t>
-  </si>
-  <si>
-    <t>English</t>
-  </si>
-  <si>
-    <t>Filipino</t>
-  </si>
-  <si>
-    <t>Mathematics</t>
-  </si>
-  <si>
-    <t>Science</t>
-  </si>
-  <si>
-    <t>Araling Panlipunan</t>
-  </si>
-  <si>
-    <t>MAPEH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edukasyon sa Pagpapakatao </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technology and Livelihood Education </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Subjects</t>
-  </si>
-  <si>
-    <t>Subject Code</t>
-  </si>
-  <si>
-    <t>ENG</t>
-  </si>
-  <si>
-    <t>FIL</t>
-  </si>
-  <si>
-    <t>MATH</t>
-  </si>
-  <si>
-    <t>SCI</t>
-  </si>
-  <si>
-    <t>AP</t>
-  </si>
-  <si>
-    <t>Music,Arts,Physical Education.Heath</t>
-  </si>
-  <si>
-    <t>TLE</t>
-  </si>
-  <si>
-    <t>ESP</t>
   </si>
   <si>
     <t>Andres Bonifacio</t>
@@ -450,13 +395,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.44140625" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -464,44 +409,44 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -511,131 +456,45 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="34.88671875" customWidth="1"/>
-    <col min="2" max="2" width="29.109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43FEE7E3-F8F3-4C2E-B6BF-3770353A5A80}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>7</v>
       </c>
@@ -649,7 +508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>8</v>
       </c>
@@ -663,7 +522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9</v>
       </c>
@@ -677,7 +536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>10</v>
       </c>
